--- a/Trabalho M2/OUTPUT_3.3.d_TESTE_MELHORES_RN/Common/Resumo_Teste_Melhores_RN.xlsx
+++ b/Trabalho M2/OUTPUT_3.3.d_TESTE_MELHORES_RN/Common/Resumo_Teste_Melhores_RN.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="62" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="93" uniqueCount="25">
   <si>
     <t>rede</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>[5 5]</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
 </sst>
 </file>
@@ -191,7 +194,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F2" s="0" t="s">
         <v>15</v>
@@ -223,10 +226,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="0" t="s">
         <v>19</v>
@@ -258,7 +261,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" s="0" t="s">
         <v>19</v>
